--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -52,7 +52,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -347,7 +347,7 @@
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
-          <a:sp3d>
+          <a:sp3d prstMaterial="warmMatte">
             <a:bevelT w="63500" h="25400"/>
           </a:sp3d>
         </a:effectStyle>
@@ -412,7 +412,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
@@ -482,7 +482,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -504,10 +504,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>12</v>
@@ -526,10 +526,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
@@ -548,10 +548,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
@@ -568,10 +568,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,6 +634,16 @@
       </c>
       <c r="B6" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>burst_duration</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -644,10 +654,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,6 +691,11 @@
           <t>attack_count</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>burst_duration</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -704,11 +719,11 @@
       <c r="B3" t="n">
         <v>0.1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.05</v>
-      </c>
       <c r="D3" t="n">
         <v>0.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -818,6 +833,9 @@
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -415,7 +415,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>last_shop_visit</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +476,9 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,7 +493,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>6</v>
@@ -493,6 +501,9 @@
       <c r="F3" t="n">
         <v>14</v>
       </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -507,13 +518,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="E4" t="n">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -529,13 +543,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -551,13 +568,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +591,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,6 +605,11 @@
           <t>min_grade</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cost_multiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -595,6 +620,9 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,6 +633,9 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,6 +646,9 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +659,9 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,6 +672,9 @@
       <c r="B6" t="n">
         <v>5</v>
       </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -643,6 +683,9 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -634,7 +634,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -700,7 +700,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,6 +739,11 @@
           <t>burst_duration</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>slow_rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -750,7 +755,7 @@
         <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +784,7 @@
         <v>0.1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D4" t="n">
         <v>0.1</v>
@@ -795,7 +800,7 @@
         <v>0.1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D5" t="n">
         <v>0.1</v>
@@ -811,7 +816,7 @@
         <v>0.1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -843,7 +848,7 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -856,7 +861,7 @@
         <v>0.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D9" t="n">
         <v>0.1</v>
@@ -872,13 +877,16 @@
         <v>0.1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -477,7 +477,7 @@
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -502,7 +502,7 @@
         <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -591,7 +591,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,19 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>attack_range</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -700,7 +713,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,6 +757,11 @@
           <t>slow_rate</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>attack_range</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -757,6 +775,9 @@
       <c r="C2" t="n">
         <v>0.1</v>
       </c>
+      <c r="I2" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -773,6 +794,9 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -789,6 +813,9 @@
       <c r="D4" t="n">
         <v>0.1</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -820,6 +847,9 @@
       </c>
       <c r="E6" t="n">
         <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -474,7 +474,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>12</v>
@@ -496,10 +496,10 @@
         <v>1.8</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>10</v>
@@ -521,10 +521,10 @@
         <v>2.6</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
         <v>8</v>
@@ -546,7 +546,7 @@
         <v>3.4</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -571,7 +571,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -634,7 +634,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -670,10 +670,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -904,19 +904,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -415,7 +415,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>weight</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>last_visit_weight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -468,17 +473,20 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>12</v>
       </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,17 +501,20 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
         <v>10</v>
       </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -518,17 +529,20 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>8</v>
       </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -543,10 +557,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -554,6 +568,9 @@
       <c r="G5" t="n">
         <v>4</v>
       </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -568,16 +585,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -812,7 +812,7 @@
         <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0.2</v>
@@ -933,7 +933,7 @@
         <v>0.2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0.2</v>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -913,7 +913,7 @@
       <c r="C9" t="n">
         <v>0.2</v>
       </c>
-      <c r="D9" t="n">
+      <c r="I9" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -929,14 +929,14 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.2</v>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0.05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -793,10 +793,10 @@
         <v>0.2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -809,13 +809,13 @@
         <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -828,13 +828,13 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -847,10 +847,10 @@
         <v>0.2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -863,13 +863,13 @@
         <v>0.2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -882,10 +882,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -898,7 +895,7 @@
         <v>0.2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9">
@@ -911,10 +908,10 @@
         <v>0.2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -936,7 +933,7 @@
         <v>0.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -809,7 +809,7 @@
         <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
         <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I4" t="n">
         <v>0.1</v>
@@ -850,7 +850,7 @@
         <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6">
@@ -882,7 +882,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8">

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -796,7 +796,7 @@
         <v>0.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="3">
@@ -815,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="4">
@@ -834,7 +834,7 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="5">
@@ -865,11 +865,8 @@
       <c r="C6" t="n">
         <v>0.15</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="7">
@@ -911,7 +908,7 @@
         <v>0.15</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -933,7 +930,7 @@
         <v>0.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -904,9 +904,6 @@
       <c r="B9" t="n">
         <v>0.2</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.15</v>
-      </c>
       <c r="I9" t="n">
         <v>0.08</v>
       </c>

--- a/Assets/02_Resources/Data/StatUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/StatUpgradeData.xlsx
@@ -878,6 +878,9 @@
       <c r="B7" t="n">
         <v>0.2</v>
       </c>
+      <c r="C7" t="n">
+        <v>0.15</v>
+      </c>
       <c r="D7" t="n">
         <v>0.05</v>
       </c>
